--- a/data/chinese/P2T3_Chapter11.xlsx
+++ b/data/chinese/P2T3_Chapter11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81DEDF7B-635C-CD4B-B693-A927415F32E8}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBB6E44-D574-C647-824F-B9582F7FCC2B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,6 +216,10 @@
   </si>
   <si>
     <t>我每天早上七點起牀。</t>
+  </si>
+  <si>
+    <t>--</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -302,7 +306,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -322,6 +326,12 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1311,8 +1321,13 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
-      <c r="B2" s="6"/>
+    <row r="2" spans="1:2" ht="16">
+      <c r="A2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>61</v>
+      </c>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="6"/>

--- a/data/chinese/P2T3_Chapter11.xlsx
+++ b/data/chinese/P2T3_Chapter11.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8FBB6E44-D574-C647-824F-B9582F7FCC2B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA80CF8-8541-E843-AC7D-6A9141762501}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -689,7 +689,7 @@
         <v>14</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -704,7 +704,7 @@
         <v>17</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5"/>
     </row>
@@ -719,7 +719,7 @@
         <v>20</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5"/>
     </row>
@@ -734,7 +734,7 @@
         <v>23</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5"/>
     </row>
@@ -749,7 +749,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -764,7 +764,7 @@
         <v>29</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5"/>
     </row>

--- a/data/chinese/P2T3_Chapter11.xlsx
+++ b/data/chinese/P2T3_Chapter11.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Github/ChineseLearning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEA80CF8-8541-E843-AC7D-6A9141762501}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F70A44-CF3F-4F43-A408-EC53B0C51723}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="61">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -216,10 +216,6 @@
   </si>
   <si>
     <t>我每天早上七點起牀。</t>
-  </si>
-  <si>
-    <t>--</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -1321,13 +1317,9 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="16">
-      <c r="A2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>61</v>
-      </c>
+    <row r="2" spans="1:2">
+      <c r="A2" s="7"/>
+      <c r="B2" s="8"/>
     </row>
     <row r="3" spans="1:2">
       <c r="B3" s="6"/>
